--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,37 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8F5"/>
+        <bgColor rgb="00D9E8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +79,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,63 +504,63 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>choose_random_item(items)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>The `choose_random_item` function selects and returns a single string at random from a given non-empty list of strings.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>- **`items`**: `List[str]` - A list of strings from which one item will be randomly selected. This list must not be empty.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to choose a random element from a list of strings. The core logic is built around Python's `random.choice()` method, which is designed to pick a single item uniformly at random from a non-empty sequence. Before attempting to select an item, the function first performs a validation check: `if not items:`. This conditional statement verifies if the provided `items` list is empty. If it is, the function immediately raises a `ValueError` with the message "items m...</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>- The input list `items` cannot be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure it is imported in the execution environment. - The selection is uniformly random, meaning every item in the list has an equal chance of being returned on each call. **Output Example**: A single string from the input list. For an input of `['apple', 'banana', 'cherry']`, a possible output is `"banana"`.</t>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>- **items** (`List[str]`): A list of strings from which to choose a random item. This list must not be empty.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to select a random element from a list. The core logic is divided into two main steps: validation and selection. First, the function validates the input list `items` by checking if it is empty with the condition `if not items:`. If the list is empty, it is impossible to choose an item, so the function raises a `ValueError` with the message "items must not be empty". This prevents potential errors from occurring in the selection process. If the list is not emp...</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure it is available in the environment. - The selection is uniformly random, meaning every item in the provided list has an equal chance of being chosen. **Output Example**: The function returns a single string that was present in the input `items` list. For an input of `['red', 'green', 'blue']`, a possible return value is `'green'`.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>shuffle_copy(items)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>- `items`: A list of integers (`List[int]`) that you want to create a shuffled copy of.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list without modifying the original data structure, a concept known as non-mutating behavior. The logic proceeds in three simple steps: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is the crucial step that prevents mutation of the original list. 2. The `random.shuffle()` method is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearranging them into a random or...</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>- The primary benefit of this function is that it is non-mutating. The original list passed as the `items` argument will not be altered. - This function depends on Python's built-in `random` module. Ensure it is imported in your script (e.g., `import random`) before calling `shuffle_copy`. - While the type hint specifies `List[int]`, the function's logic will work correctly with lists containing other data types, such as strings, floats, or mixed types. **Output Example**: A new list with the...</t>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function creates and returns a new list containing the elements of the input list in a randomized order, without altering the original list.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>- **`items`** (List[int]): A list of integers to be shuffled.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to get a shuffled version of a list while preserving the original. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a crucial step to prevent modification of the original list that was passed as an argument. 2. The `random.shuffle()` function is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearranging them into a random sequence. 3. Finally, the...</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>- **Non-Mutating:** The primary feature of this function is that it does not change the input `items` list. It operates on a copy, leaving the original data intact. - **Random Module Dependency:** This function depends on Python's built-in `random` module. Ensure it is imported (e.g., `import random`) in the file where this function is used. - **Shallow Copy:** The function creates a shallow copy. If the list contains mutable objects (like other lists or dictionaries), the objects themselves ...</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -465,7 +465,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
@@ -510,27 +510,27 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>choose_random_item(items)</t>
+          <t>choose_random_item</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single random item from a given list of strings.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>- **items** (`List[str]`): A list of strings from which to choose a random item. This list must not be empty.</t>
+          <t>- **`items`** (`List[str]`): A non-empty list of strings from which a random item will be chosen.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to select a random element from a list. The core logic is divided into two main steps: validation and selection. First, the function validates the input list `items` by checking if it is empty with the condition `if not items:`. If the list is empty, it is impossible to choose an item, so the function raises a `ValueError` with the message "items must not be empty". This prevents potential errors from occurring in the selection process. If the list is not emp...</t>
+          <t>This function provides a simple way to get a random element from a list. The core logic is handled by Python's built-in `random.choice()` method. Before attempting to select an item, the function first validates the input list `items`. It checks if the list is empty using the condition `if not items:`. If the list is found to be empty, the function immediately raises a `ValueError` with the message "items must not be empty". This prevents runtime errors that would occur if `random.choice()` w...</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure it is available in the environment. - The selection is uniformly random, meaning every item in the provided list has an equal chance of being chosen. **Output Example**: The function returns a single string that was present in the input `items` list. For an input of `['red', 'green', 'blue']`, a possible return value is `'green'`.</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function relies on Python's `random` module. Ensure it is imported in the environment where the function is used. - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen on any given call. **Output Example**: A single string from the input list.</t>
         </is>
       </c>
     </row>
@@ -540,27 +540,27 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>shuffle_copy(items)</t>
+          <t>shuffle_copy</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function creates and returns a new list containing the elements of the input list in a randomized order, without altering the original list.</t>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>- **`items`** (List[int]): A list of integers to be shuffled.</t>
+          <t>- **`items`** (`List[int]`): The list of integers that you want to create a shuffled copy of.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a safe way to get a shuffled version of a list while preserving the original. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a crucial step to prevent modification of the original list that was passed as an argument. 2. The `random.shuffle()` function is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearranging them into a random sequence. 3. Finally, the...</t>
+          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process involves three main steps: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a critical step that isolates the operation from the original list, preventing its mutation. 2. The `random.shuffle()` method is then called on this `copy`. This function shuffles the elements of the list in-place, rearranging them into a random order. 3. Finally, the ...</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- **Non-Mutating:** The primary feature of this function is that it does not change the input `items` list. It operates on a copy, leaving the original data intact. - **Random Module Dependency:** This function depends on Python's built-in `random` module. Ensure it is imported (e.g., `import random`) in the file where this function is used. - **Shallow Copy:** The function creates a shallow copy. If the list contains mutable objects (like other lists or dictionaries), the objects themselves ...</t>
+          <t>- This function is non-mutating. The original list passed as the `items` parameter will not be modified. - The function requires the `random` module to be imported in the script where it is used. - The order of elements in the returned list is non-deterministic and will likely be different on each execution. **Output Example**: A possible return value for an input of `[1, 2, 3]` could be:</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -515,22 +515,22 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single random item from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single random element from a given list of strings.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>- **`items`** (`List[str]`): A non-empty list of strings from which a random item will be chosen.</t>
+          <t>- **`items`** `List[str]`: A list of strings to choose from. This list must not be empty.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to get a random element from a list. The core logic is handled by Python's built-in `random.choice()` method. Before attempting to select an item, the function first validates the input list `items`. It checks if the list is empty using the condition `if not items:`. If the list is found to be empty, the function immediately raises a `ValueError` with the message "items must not be empty". This prevents runtime errors that would occur if `random.choice()` w...</t>
+          <t>This function provides a safe way to select a single item uniformly at random from a list. The function first validates the input `items` list. It checks if the list is empty using the `if not items:` condition. If the list is found to be empty, the function immediately stops execution and raises a `ValueError` with the message "items must not be empty". This prevents potential errors from attempting to choose an item from an empty collection. If the `items` list is not empty, the function pr...</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function relies on Python's `random` module. Ensure it is imported in the environment where the function is used. - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen on any given call. **Output Example**: A single string from the input list.</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the execution environment. - The selection is uniformly random, meaning every item in the input list has an equal chance of being chosen. **Output Example**: If the input list is `['red', 'green', 'blue']`, a possible return value is `'green'`.</t>
         </is>
       </c>
     </row>
@@ -545,22 +545,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
+          <t>The `shuffle_copy` function returns a new list containing the same elements as the input list but in a randomized order, without altering the original list.</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>- **`items`** (`List[int]`): The list of integers that you want to create a shuffled copy of.</t>
+          <t>- `items`: `List[int]` - A list of integers to be shuffled.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process involves three main steps: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a critical step that isolates the operation from the original list, preventing its mutation. 2. The `random.shuffle()` method is then called on this `copy`. This function shuffles the elements of the list in-place, rearranging them into a random order. 3. Finally, the ...</t>
+          <t>This function provides a safe way to shuffle a list by operating on a copy rather than the original data. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a crucial step to prevent mutation of the original list provided by the caller. 2. The `random.shuffle()` function is then called on this `copy`. The `random.shuffle()` method shuffles the sequence of the list *in-place*, rearranging the order of its elements randomly. 3. ...</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- This function is non-mutating. The original list passed as the `items` parameter will not be modified. - The function requires the `random` module to be imported in the script where it is used. - The order of elements in the returned list is non-deterministic and will likely be different on each execution. **Output Example**: A possible return value for an input of `[1, 2, 3]` could be:</t>
+          <t>- **Non-Mutating:** The primary feature of this function is that it does not modify the original list passed as an argument. It returns a new, shuffled list. - **Dependency:** This function requires the `random` module to be imported in the script where it is defined. - **Randomness:** The order of elements in the returned list is random. Calling the function multiple times with the same input list will likely result in different outputs. - **Data Integrity:** The returned list will contain t...</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -515,22 +515,22 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single random element from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single random item from a given list of strings.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>- **`items`** `List[str]`: A list of strings to choose from. This list must not be empty.</t>
+          <t>- **`items`** (`List[str]`): A non-empty list of strings from which a random item will be chosen.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to select a single item uniformly at random from a list. The function first validates the input `items` list. It checks if the list is empty using the `if not items:` condition. If the list is found to be empty, the function immediately stops execution and raises a `ValueError` with the message "items must not be empty". This prevents potential errors from attempting to choose an item from an empty collection. If the `items` list is not empty, the function pr...</t>
+          <t>This function provides a safe way to pick a random element from a list. It first performs a validation check to ensure the input list `items` is not empty. If the list is empty, the function raises a `ValueError` to prevent runtime errors that would occur from attempting to choose an item from an empty sequence. If the list contains one or more items, the function then utilizes the `random.choice()` method from Python's `random` module. This method selects a single item uniformly at random fr...</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the execution environment. - The selection is uniformly random, meaning every item in the input list has an equal chance of being chosen. **Output Example**: If the input list is `['red', 'green', 'blue']`, a possible return value is `'green'`.</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen. - This function depends on Python's built-in `random` module, which must be imported in the script for `random.choice()` to be available. **Output Example**: A single string from the provided list. For a list `['red', 'green', 'blue']`, a possible output is `'green'`.</t>
         </is>
       </c>
     </row>
@@ -545,22 +545,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new list containing the same elements as the input list but in a randomized order, without altering the original list.</t>
+          <t>The `shuffle_copy` function returns a shuffled copy of a given list of integers without modifying the original list.</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>- `items`: `List[int]` - A list of integers to be shuffled.</t>
+          <t>- `items` (List[int]): A list of integers to be shuffled.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list by operating on a copy rather than the original data. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a crucial step to prevent mutation of the original list provided by the caller. 2. The `random.shuffle()` function is then called on this `copy`. The `random.shuffle()` method shuffles the sequence of the list *in-place*, rearranging the order of its elements randomly. 3. ...</t>
+          <t>This function provides a safe way to get a randomized version of a list while preserving the original data. The logic proceeds as follows: 1. A shallow copy of the input `items` list is created by calling `list(items)`. This new list is stored in a `copy` variable, ensuring that the original list passed to the function remains unchanged. 2. The `random.shuffle()` function is then called on this `copy`. The `random.shuffle()` method shuffles the sequence of elements in the `copy` list in-place...</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- **Non-Mutating:** The primary feature of this function is that it does not modify the original list passed as an argument. It returns a new, shuffled list. - **Dependency:** This function requires the `random` module to be imported in the script where it is defined. - **Randomness:** The order of elements in the returned list is random. Calling the function multiple times with the same input list will likely result in different outputs. - **Data Integrity:** The returned list will contain t...</t>
+          <t>- This function does not modify the original `items` list. It operates on and returns a new, separate list. - The function depends on Python's built-in `random` module. Ensure this module is imported (`import random`) in the file where `shuffle_copy` is defined or used. - Although the type hint specifies `List[int]`, the underlying logic will work correctly with a list containing elements of any type (e.g., strings, floats, or objects). **Output Example**: A possible return value for an input...</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Documentation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,44 +461,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Function No</t>
+          <t>Item No</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Function Name</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Parameters</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Usage Notes</t>
         </is>
@@ -510,27 +516,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>choose_random_item</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>The `choose_random_item` function selects and returns a single random item from a given list of strings.</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>- **`items`** (`List[str]`): A non-empty list of strings from which a random item will be chosen.</t>
-        </is>
-      </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to pick a random element from a list. It first performs a validation check to ensure the input list `items` is not empty. If the list is empty, the function raises a `ValueError` to prevent runtime errors that would occur from attempting to choose an item from an empty sequence. If the list contains one or more items, the function then utilizes the `random.choice()` method from Python's `random` module. This method selects a single item uniformly at random fr...</t>
+          <t>- **items** `List[str]`: A non-empty list of strings from which a single item will be randomly selected.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen. - This function depends on Python's built-in `random` module, which must be imported in the script for `random.choice()` to be available. **Output Example**: A single string from the provided list. For a list `['red', 'green', 'blue']`, a possible output is `'green'`.</t>
+          <t>This function provides a simple way to choose one element uniformly at random from a sequence. The function first performs a validation check to ensure the input list `items` is not empty. If the list is empty, it immediately raises a `ValueError` with the message "items must not be empty" to prevent runtime errors and enforce the requirement of a non-empty sequence. If the list contains one or more items, the function then utilizes the `random.choice()` method. This method takes the `items` ...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>- This function requires the `random` module to be imported in the script. - The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen on any given call. **Output Example**: The function returns a single string. For an input of `['red', 'green', 'blue']`, a possible return value would be:</t>
         </is>
       </c>
     </row>
@@ -540,27 +551,102 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>choose_random_item</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>The `choose_random_item` function randomly selects and returns a single string from a given list of strings.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>- **`items`** (`List[str]`): A list of strings from which one item will be randomly chosen.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a straightforward way to get a random element from a list. It takes a single argument, `items`, which is expected to be a list of strings. Internally, the function utilizes Python's built-in `random` module. It calls the `random.choice()` method, passing the input `items` list to it. The `random.choice()` method is specifically designed to return a randomly selected element from a non-empty sequence. The element chosen by `random.choice()` is then returned as the output...</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>- The input list `items` must not be empty. Providing an empty list will cause a `IndexError` to be raised by the underlying `random.choice()` method. - While the type hint specifies `List[str]`, the core `random.choice()` function can operate on any non-empty sequence (like a tuple or a list of other types). However, for intended use according to the function's signature, a list of strings should be provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>shuffle_copy</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function returns a shuffled copy of a given list of integers without modifying the original list.</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>- `items` (List[int]): A list of integers to be shuffled.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to get a randomized version of a list while preserving the original data. The logic proceeds as follows: 1. A shallow copy of the input `items` list is created by calling `list(items)`. This new list is stored in a `copy` variable, ensuring that the original list passed to the function remains unchanged. 2. The `random.shuffle()` function is then called on this `copy`. The `random.shuffle()` method shuffles the sequence of elements in the `copy` list in-place...</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>- This function does not modify the original `items` list. It operates on and returns a new, separate list. - The function depends on Python's built-in `random` module. Ensure this module is imported (`import random`) in the file where `shuffle_copy` is defined or used. - Although the type hint specifies `List[int]`, the underlying logic will work correctly with a list containing elements of any type (e.g., strings, floats, or objects). **Output Example**: A possible return value for an input...</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>- **`items`** `List[int]`: A list of integers to be shuffled. The original list will not be modified.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process is straightforward and consists of two main steps. First, the function creates a shallow copy of the input `items` list by calling `list(items)`. This is a critical step that prevents mutation of the original list passed to the function. The new list is stored in a local variable named `copy`. Next, it utilizes the `random.shuffle()` method, which shuffles the elements of the `copy` l...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>- The primary advantage of this function is that it is non-mutating. The input list `items` is guaranteed to remain in its original order after the function call. - This function depends on Python's built-in `random` module. Ensure this module is imported (e.g., `import random`) in the scope where `shuffle_copy` is defined and used. - While the type hint specifies `List[int]`, the function's logic will work correctly with lists containing any type of element (e.g., strings, floats, or mixed t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>shuffle_copy</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function creates and returns a new list containing the same elements as the input list but in a random order.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>- `items`: `List[int]` | The list of integers to be copied and shuffled.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a non-destructive way to shuffle a list. The core logic involves two main steps: 1. **Create a Copy**: The function first creates a shallow copy of the input `items` list. This is a critical step to ensure that the original list passed to the function remains unchanged. This is typically achieved using a method like `items.copy()`. 2. **Shuffle the Copy**: The newly created list is then shuffled in-place using a randomization algorithm, such as the Fisher-Yates shuffle....</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>- This function is non-destructive; it does not alter the original input list `items`. - A new list object is created and returned with each call. - The order of elements in the returned list is random. Calling the function multiple times with the same input will likely produce different results.</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -531,17 +531,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>- **items** `List[str]`: A non-empty list of strings from which a single item will be randomly selected.</t>
+          <t>- **`items`** (`List[str]`): A list of strings to choose from. This list must not be empty.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to choose one element uniformly at random from a sequence. The function first performs a validation check to ensure the input list `items` is not empty. If the list is empty, it immediately raises a `ValueError` with the message "items must not be empty" to prevent runtime errors and enforce the requirement of a non-empty sequence. If the list contains one or more items, the function then utilizes the `random.choice()` method. This method takes the `items` ...</t>
+          <t>This function provides a safe way to select a random element from a list of strings. The core logic involves two main steps: 1. **Validation**: The function first checks if the provided `items` list is empty using the condition `if not items:`. This is a crucial safeguard to prevent errors in the subsequent steps. If the list is empty, the function raises a `ValueError` with the message "items must not be empty", immediately halting execution and informing the user of the invalid input. 2. **...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function requires the `random` module to be imported in the script. - The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen on any given call. **Output Example**: The function returns a single string. For an input of `['red', 'green', 'blue']`, a possible return value would be:</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the environment where this function is used (e.g., `import random`). - The selection is uniformly random, meaning each item in the list has an equal chance of being chosen on any given call. **Output Example**: A single string element from the input list. For an input of `["red", "green", "blue"]`, a possible ...</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function randomly selects and returns a single string from a given list of strings.</t>
+          <t>The `choose_random_item` function randomly selects and returns a single string element from a given list of strings.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- **`items`** (`List[str]`): A list of strings from which one item will be randomly chosen.</t>
+          <t>- `items`: `List[str]` - A list of strings from which one item will be randomly chosen.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to get a random element from a list. It takes a single argument, `items`, which is expected to be a list of strings. Internally, the function utilizes Python's built-in `random` module. It calls the `random.choice()` method, passing the input `items` list to it. The `random.choice()` method is specifically designed to return a randomly selected element from a non-empty sequence. The element chosen by `random.choice()` is then returned as the output...</t>
+          <t>This function is designed to perform a random selection from a collection of items. It accepts a single argument, `items`, which is expected to be a list of strings. Internally, the function utilizes a random selection algorithm to pick one element from the input `items` list. The most common implementation in Python would involve using the `random.choice()` method from the standard `random` library, which is purpose-built for this task. After selecting an item, the function returns it as a s...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will cause a `IndexError` to be raised by the underlying `random.choice()` method. - While the type hint specifies `List[str]`, the core `random.choice()` function can operate on any non-empty sequence (like a tuple or a list of other types). However, for intended use according to the function's signature, a list of strings should be provided.</t>
+          <t>- The input list `items` must not be empty. Passing an empty list will result in a `ValueError` or `IndexError`, depending on the implementation. - The function is non-deterministic. Calling it multiple times with the same list will likely produce different results. - As per the type hint `List[str]`, the function is specifically designed to work with lists of strings.</t>
         </is>
       </c>
     </row>
@@ -596,22 +596,22 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list without altering the original list.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- **`items`** `List[int]`: A list of integers to be shuffled. The original list will not be modified.</t>
+          <t>* `items` (`List[int]`): A list of integers that will be copied and shuffled.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process is straightforward and consists of two main steps. First, the function creates a shallow copy of the input `items` list by calling `list(items)`. This is a critical step that prevents mutation of the original list passed to the function. The new list is stored in a local variable named `copy`. Next, it utilizes the `random.shuffle()` method, which shuffles the elements of the `copy` l...</t>
+          <t>This function provides a safe way to shuffle a list by ensuring the original data structure remains untouched. The process is executed in three main steps: 1. A shallow copy of the input `items` list is created using `list(items)`. This new list is stored in a variable named `copy`. This step is crucial for preventing mutation of the original list passed to the function. 2. The `random.shuffle()` method is then called on the `copy`. This function shuffles the elements of the `copy` list in-pl...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The primary advantage of this function is that it is non-mutating. The input list `items` is guaranteed to remain in its original order after the function call. - This function depends on Python's built-in `random` module. Ensure this module is imported (e.g., `import random`) in the scope where `shuffle_copy` is defined and used. - While the type hint specifies `List[int]`, the function's logic will work correctly with lists containing any type of element (e.g., strings, floats, or mixed t...</t>
+          <t>- This function is non-mutating, meaning the original list you pass as an argument will not be changed. - The function relies on Python's built-in `random` module. Ensure this module is imported in your script before calling the function. - Due to the nature of random shuffling, calling the function multiple times with the same input list will likely produce a different-ordered list each time. **Output Example**: A possible return value for an input of `[1, 2, 3, 4, 5]`.</t>
         </is>
       </c>
     </row>
@@ -631,22 +631,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function creates and returns a new list containing the same elements as the input list but in a random order.</t>
+          <t>The `shuffle_copy` function creates a shuffled copy of a list of integers, leaving the original list unchanged.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- `items`: `List[int]` | The list of integers to be copied and shuffled.</t>
+          <t>- `items`: `List[int]` - The input list of integers to be copied and shuffled.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a non-destructive way to shuffle a list. The core logic involves two main steps: 1. **Create a Copy**: The function first creates a shallow copy of the input `items` list. This is a critical step to ensure that the original list passed to the function remains unchanged. This is typically achieved using a method like `items.copy()`. 2. **Shuffle the Copy**: The newly created list is then shuffled in-place using a randomization algorithm, such as the Fisher-Yates shuffle....</t>
+          <t>This function provides a non-destructive way to shuffle a list. It operates by first creating a shallow copy of the input `items` list. This initial step is crucial as it ensures that the original list passed to the function is not altered. After creating the copy, the function shuffles the elements of the new list in-place, rearranging them into a random order. Finally, it returns this newly created and shuffled list. The original `items` list remains in its initial order.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- This function is non-destructive; it does not alter the original input list `items`. - A new list object is created and returned with each call. - The order of elements in the returned list is random. Calling the function multiple times with the same input will likely produce different results.</t>
+          <t>- This function does not modify the original list. It returns a new, shuffled list. - The shuffling is pseudo-random. For reproducible results, you can seed Python's random number generator using `random.seed()` before calling this function. - Although the type hint specifies `List[int]`, the underlying logic works with lists containing elements of any type.</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -531,17 +531,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>- **`items`** (`List[str]`): A list of strings to choose from. This list must not be empty.</t>
+          <t>* **items** (`List[str]`): A list of strings from which to choose a single random item. This list must not be empty.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to select a random element from a list of strings. The core logic involves two main steps: 1. **Validation**: The function first checks if the provided `items` list is empty using the condition `if not items:`. This is a crucial safeguard to prevent errors in the subsequent steps. If the list is empty, the function raises a `ValueError` with the message "items must not be empty", immediately halting execution and informing the user of the invalid input. 2. **...</t>
+          <t>This function provides a simple way to get a random element from a list of strings. The core logic is handled in two main steps: 1. **Input Validation**: The function first checks if the provided `items` list is empty using the `if not items:` condition. If the list is empty, it immediately raises a `ValueError` with the message "items must not be empty". This prevents the program from attempting to choose an item from a non-existent collection, which would otherwise cause an error. 2. **Rand...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the environment where this function is used (e.g., `import random`). - The selection is uniformly random, meaning each item in the list has an equal chance of being chosen on any given call. **Output Example**: A single string element from the input list. For an input of `["red", "green", "blue"]`, a possible ...</t>
+          <t>- This function requires the `random` module to be imported in the script where it is defined. - Providing an empty list as the `items` parameter will result in a `ValueError`. Always ensure the list contains at least one element before calling this function. - The selection is uniformly random, meaning each item in the list has an equal chance of being chosen on any given call. **Output Example**: A single string from the input list. For a list `['apple', 'banana', 'cherry']`, a possible ret...</t>
         </is>
       </c>
     </row>
@@ -556,97 +556,27 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>choose_random_item</t>
+          <t>shuffle_copy</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function randomly selects and returns a single string element from a given list of strings.</t>
+          <t>The `shuffle_copy` function returns a shuffled copy of a given list of integers without modifying the original list.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- `items`: `List[str]` - A list of strings from which one item will be randomly chosen.</t>
+          <t>- `items`: `List[int]` - A list of integers to be copied and shuffled.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function is designed to perform a random selection from a collection of items. It accepts a single argument, `items`, which is expected to be a list of strings. Internally, the function utilizes a random selection algorithm to pick one element from the input `items` list. The most common implementation in Python would involve using the `random.choice()` method from the standard `random` library, which is purpose-built for this task. After selecting an item, the function returns it as a s...</t>
+          <t>This function provides a safe, non-destructive way to shuffle a list by operating on a copy rather than the original data. The logic proceeds as follows: 1. A shallow copy of the input `items` list is created using the expression `copy = list(items)`. This step is crucial as it ensures that the original list passed to the function remains unchanged. 2. The `random.shuffle()` function is then called on the `copy`. This standard Python function shuffles the elements of the list in-place, rearra...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Passing an empty list will result in a `ValueError` or `IndexError`, depending on the implementation. - The function is non-deterministic. Calling it multiple times with the same list will likely produce different results. - As per the type hint `List[str]`, the function is specifically designed to work with lists of strings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>shuffle_copy</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list without altering the original list.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>* `items` (`List[int]`): A list of integers that will be copied and shuffled.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list by ensuring the original data structure remains untouched. The process is executed in three main steps: 1. A shallow copy of the input `items` list is created using `list(items)`. This new list is stored in a variable named `copy`. This step is crucial for preventing mutation of the original list passed to the function. 2. The `random.shuffle()` method is then called on the `copy`. This function shuffles the elements of the `copy` list in-pl...</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>- This function is non-mutating, meaning the original list you pass as an argument will not be changed. - The function relies on Python's built-in `random` module. Ensure this module is imported in your script before calling the function. - Due to the nature of random shuffling, calling the function multiple times with the same input list will likely produce a different-ordered list each time. **Output Example**: A possible return value for an input of `[1, 2, 3, 4, 5]`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>shuffle_copy</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function creates a shuffled copy of a list of integers, leaving the original list unchanged.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>- `items`: `List[int]` - The input list of integers to be copied and shuffled.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a non-destructive way to shuffle a list. It operates by first creating a shallow copy of the input `items` list. This initial step is crucial as it ensures that the original list passed to the function is not altered. After creating the copy, the function shuffles the elements of the new list in-place, rearranging them into a random order. Finally, it returns this newly created and shuffled list. The original `items` list remains in its initial order.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>- This function does not modify the original list. It returns a new, shuffled list. - The shuffling is pseudo-random. For reproducible results, you can seed Python's random number generator using `random.seed()` before calling this function. - Although the type hint specifies `List[int]`, the underlying logic works with lists containing elements of any type.</t>
+          <t>- The primary feature of this function is that it is non-mutating; the input list `items` is not altered. - This function requires the `random` module to be imported (e.g., `import random`) in the script where it is used. - The order of elements in the returned list is non-deterministic due to the nature of the random shuffling algorithm. - The function creates a shallow copy. For a list of simple types like integers, this is perfectly safe. **Output Example**: A possible return value for an ...</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -531,17 +531,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>* **items** (`List[str]`): A list of strings from which to choose a single random item. This list must not be empty.</t>
+          <t>- `items`: `List[str]` - A list of strings from which a single item will be randomly selected.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to get a random element from a list of strings. The core logic is handled in two main steps: 1. **Input Validation**: The function first checks if the provided `items` list is empty using the `if not items:` condition. If the list is empty, it immediately raises a `ValueError` with the message "items must not be empty". This prevents the program from attempting to choose an item from a non-existent collection, which would otherwise cause an error. 2. **Rand...</t>
+          <t>This function provides a simple way to get a random element from a list. The core logic is built around Python's standard `random` module. First, the function validates the input `items` list. It checks if the list is empty using the condition `if not items:`. If the list is found to be empty, the function immediately stops execution and raises a `ValueError` with the message "items must not be empty". This check is crucial to prevent errors from the underlying `random.choice` function, which...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function requires the `random` module to be imported in the script where it is defined. - Providing an empty list as the `items` parameter will result in a `ValueError`. Always ensure the list contains at least one element before calling this function. - The selection is uniformly random, meaning each item in the list has an equal chance of being chosen on any given call. **Output Example**: A single string from the input list. For a list `['apple', 'banana', 'cherry']`, a possible ret...</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the script where this function is called. - The selection is uniformly random, meaning every item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list. For an input list `['apple', 'banana', 'cherry']`, a possible output is `'banana'`.</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a shuffled copy of a given list of integers without modifying the original list.</t>
+          <t>The `shuffle_copy` function returns a shuffled copy of a given list without modifying the original input list.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- `items`: `List[int]` - A list of integers to be copied and shuffled.</t>
+          <t>* `items` (`List[int]`): A list of integers to be copied and shuffled.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a safe, non-destructive way to shuffle a list by operating on a copy rather than the original data. The logic proceeds as follows: 1. A shallow copy of the input `items` list is created using the expression `copy = list(items)`. This step is crucial as it ensures that the original list passed to the function remains unchanged. 2. The `random.shuffle()` function is then called on the `copy`. This standard Python function shuffles the elements of the list in-place, rearra...</t>
+          <t>This function provides a non-destructive way to shuffle the elements of a list. The internal logic operates in three steps: 1. First, it creates a shallow copy of the input `items` list by calling `list(items)`. This ensures that any subsequent modifications do not affect the original list provided by the user. 2. Next, it uses the `random.shuffle()` method to shuffle the newly created `copy` list. The `random.shuffle()` function modifies the sequence in-place, rearranging its elements into a...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The primary feature of this function is that it is non-mutating; the input list `items` is not altered. - This function requires the `random` module to be imported (e.g., `import random`) in the script where it is used. - The order of elements in the returned list is non-deterministic due to the nature of the random shuffling algorithm. - The function creates a shallow copy. For a list of simple types like integers, this is perfectly safe. **Output Example**: A possible return value for an ...</t>
+          <t>- This function is guaranteed not to mutate the original `items` list. It is a "safe" operation for shuffling. - The function requires the `random` module to be imported in the script where it is used. - Although the type hint specifies `List[int]`, the function works correctly with lists containing elements of any data type (e.g., `str`, `float`, objects). **Output Example**: The returned list will have the same length and elements as the input list. For an input of `[1, 2, 3]`, a possible o...</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single random item from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random string from a provided list of strings.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>- `items`: `List[str]` - A list of strings from which a single item will be randomly selected.</t>
+          <t>* `items` (`List[str]`): A list of strings from which to choose a random item. This list must not be empty.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to get a random element from a list. The core logic is built around Python's standard `random` module. First, the function validates the input `items` list. It checks if the list is empty using the condition `if not items:`. If the list is found to be empty, the function immediately stops execution and raises a `ValueError` with the message "items must not be empty". This check is crucial to prevent errors from the underlying `random.choice` function, which...</t>
+          <t>This function is designed to safely select one random element from a list. It first performs a validation check to ensure the input list `items` is not empty. If the list is found to be empty using the `if not items:` condition, the function immediately stops execution and raises a `ValueError` with the message "items must not be empty". This prevents errors that would occur when trying to choose from an empty collection. If the list is valid (i.e., contains at least one item), the function t...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the script where this function is called. - The selection is uniformly random, meaning every item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list. For an input list `['apple', 'banana', 'cherry']`, a possible output is `'banana'`.</t>
+          <t>- The input list `items` must contain at least one element. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the scope where `choose_random_item` is defined. - Each item in the list has an equal probability of being selected. **Output Example**: For an input of `['red', 'green', 'blue']`, a possible output is `'green'`. The actual output will be one of the strings from the list, chosen randomly.</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a shuffled copy of a given list without modifying the original input list.</t>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>* `items` (`List[int]`): A list of integers to be copied and shuffled.</t>
+          <t>- `items`: `List[int]` - The list of integers to be shuffled.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a non-destructive way to shuffle the elements of a list. The internal logic operates in three steps: 1. First, it creates a shallow copy of the input `items` list by calling `list(items)`. This ensures that any subsequent modifications do not affect the original list provided by the user. 2. Next, it uses the `random.shuffle()` method to shuffle the newly created `copy` list. The `random.shuffle()` function modifies the sequence in-place, rearranging its elements into a...</t>
+          <t>This function provides a safe way to shuffle a list without altering the original data structure. The core logic involves three main steps: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a critical step that allocates new memory for a new list, preventing any modifications to the original list passed to the function. 2. The `random.shuffle(copy)` function is then called. This function, from Python's standard `random` module, shuffles the elements of...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function is guaranteed not to mutate the original `items` list. It is a "safe" operation for shuffling. - The function requires the `random` module to be imported in the script where it is used. - Although the type hint specifies `List[int]`, the function works correctly with lists containing elements of any data type (e.g., `str`, `float`, objects). **Output Example**: The returned list will have the same length and elements as the input list. For an input of `[1, 2, 3]`, a possible o...</t>
+          <t>- The primary benefit of this function is that it is non-mutating. The original list you pass as an argument will not be modified. - This function requires the `random` module to be imported into the script where it is used (i.e., `import random`). - Although the type hint specifies `List[int]`, the function will work correctly with lists containing elements of any type (e.g., strings, floats, or other objects) as `random.shuffle` is generic. **Output Example**: The function returns a new lis...</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random string from a provided list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>* `items` (`List[str]`): A list of strings from which to choose a random item. This list must not be empty.</t>
+          <t>- `items` (List[str]): A non-empty list of strings from which to choose a random item.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function is designed to safely select one random element from a list. It first performs a validation check to ensure the input list `items` is not empty. If the list is found to be empty using the `if not items:` condition, the function immediately stops execution and raises a `ValueError` with the message "items must not be empty". This prevents errors that would occur when trying to choose from an empty collection. If the list is valid (i.e., contains at least one item), the function t...</t>
+          <t>This function provides a safe way to select a random element from a list. It first performs a validation check to ensure the input list `items` is not empty. If the list is empty, the function raises a `ValueError` with the message `"items must not be empty"` to prevent runtime errors from downstream operations. If the list contains one or more elements, the function then utilizes the `random.choice()` method from Python's `random` module. This method selects a single item from the sequence a...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must contain at least one element. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the scope where `choose_random_item` is defined. - Each item in the list has an equal probability of being selected. **Output Example**: For an input of `['red', 'green', 'blue']`, a possible output is `'green'`. The actual output will be one of the strings from the list, chosen randomly.</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the environment where this function is used. - The type hint specifies the input should be a list of strings (`List[str]`). While `random.choice` works on any non-empty sequence, this function's explicit contract is for a list of strings. **Output Example**: A single string from the input list. For example, if...</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
+          <t>The `shuffle_copy` function returns a new list containing the same elements as the input list but in a randomized order, without modifying the original list.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- `items`: `List[int]` - The list of integers to be shuffled.</t>
+          <t>- `items`: `List[int]` - A list of integers that will be copied and shuffled.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list without altering the original data structure. The core logic involves three main steps: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a critical step that allocates new memory for a new list, preventing any modifications to the original list passed to the function. 2. The `random.shuffle(copy)` function is then called. This function, from Python's standard `random` module, shuffles the elements of...</t>
+          <t>This function provides a safe way to shuffle a list without causing side effects. The logic proceeds in three steps: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is the key step that ensures the original list passed to the function remains unchanged. 2. The standard library's `random.shuffle()` function is then called on the `copy`. This function shuffles the elements of the list *in-place*, rearranging the `copy` into a random permutation. 3. Finall...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The primary benefit of this function is that it is non-mutating. The original list you pass as an argument will not be modified. - This function requires the `random` module to be imported into the script where it is used (i.e., `import random`). - Although the type hint specifies `List[int]`, the function will work correctly with lists containing elements of any type (e.g., strings, floats, or other objects) as `random.shuffle` is generic. **Output Example**: The function returns a new lis...</t>
+          <t>- **Non-mutating:** The primary feature of this function is that it does not alter the original input list. It operates on a copy. - **Dependency:** This function requires the `random` module to be imported in the script where it is defined. - **Randomness:** The shuffle is pseudo-random. For reproducible results during testing, you can set the seed for the random number generator using `random.seed()` before calling this function. **Output Example**: A new list object containing the same ele...</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -461,12 +461,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random element from a given list of strings.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>- `items` (List[str]): A non-empty list of strings from which to choose a random item.</t>
+          <t>- **`items`** (`List[str]`): A list of strings from which one item will be randomly selected. This list must not be empty.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to select a random element from a list. It first performs a validation check to ensure the input list `items` is not empty. If the list is empty, the function raises a `ValueError` with the message `"items must not be empty"` to prevent runtime errors from downstream operations. If the list contains one or more elements, the function then utilizes the `random.choice()` method from Python's `random` module. This method selects a single item from the sequence a...</t>
+          <t>This function provides a safe way to choose a random item from a list. The logic proceeds as follows: 1. It first performs a validation check to determine if the input list `items` is empty. 2. If the list is empty, the condition `if not items:` evaluates to `True`, and the function raises a `ValueError` with the message "items must not be empty". This prevents errors that would otherwise occur when trying to select an item from an empty sequence. 3. If the list contains one or more elements,...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the environment where this function is used. - The type hint specifies the input should be a list of strings (`List[str]`). While `random.choice` works on any non-empty sequence, this function's explicit contract is for a list of strings. **Output Example**: A single string from the input list. For example, if...</t>
+          <t>- The input list `items` must contain at least one element. Providing an empty list will result in a `ValueError`. - This function requires the `random` module to be imported in the script where it is used. - The selection is uniform, meaning every item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list. For example: `'banana'`</t>
         </is>
       </c>
     </row>
@@ -556,27 +556,167 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
+          <t>second_largest(nums)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>The `second_largest` function finds and returns the second-largest number from a list of numbers.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>- `nums` (list): A list of numbers (integers or floats) from which to find the second-largest value.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a reliable way to determine the second-largest value in a list by first removing any duplicate entries. The function begins by converting the input `nums` list into a `set` to eliminate duplicate values, and then converts it back into a `list` named `unique_nums`. Next, it sorts `unique_nums` in ascending order using the `sort()` method. After sorting, the largest number will be at the end of the list, and the second-largest will be the second-to-last element. Finally, ...</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>- The function correctly handles lists with duplicate numbers by considering only the unique values. - If the input list contains fewer than two unique numbers (e.g., `[5]`, `[8, 8, 8]`, or `[]`), the function will return `None`. - The input list can contain a mix of integers and floats. - The original input list `nums` is not modified by the function. **Output Example**: A numeric value (integer or float) or `None`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>count_even_odd(numbers)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>The `count_even_odd` function iterates through a list of integers and counts how many are even and how many are odd.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>* **`numbers`** (`list` of `int`): A list or other iterable containing the integers to be evaluated.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a straightforward way to tally even and odd numbers within a collection. It initializes two counter variables, `even` and `odd`, to zero. The function then enters a `for` loop that iterates over each element, referred to as `num`, in the input `numbers` list. Inside the loop, it uses the modulo operator (`%`) to check if `num` is divisible by 2. - If `num % 2` equals `0`, the number is even, and the `even` counter is incremented by one. - If the result is not `0`, the n...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>- The input `numbers` must be an iterable containing numeric types that support the modulo operator. - The function will raise a `TypeError` if it encounters a non-numeric type within the list during the check. - The returned value is always a tuple of two integers: `(count_of_even, count_of_odd)`. **Output Example**: A tuple containing two integers. `(2, 3)`</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>fibonacci</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>- `n` (int): The 0-based index of the Fibonacci number to be computed.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a memory-efficient way to calculate a Fibonacci number. The Fibonacci sequence starts with 0 and 1, and each subsequent number is the sum of the two preceding ones (e.g., 0, 1, 1, 2, 3, 5, 8...). The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbe...</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>- The index `n` is 0-based. For example, `fibonacci(0)` returns `0`, and `fibonacci(1)` returns `1`. - The function will raise a `ValueError` if a negative integer is provided as the argument. - This iterative implementation is efficient for large values of `n` as it avoids the overhead and potential stack overflow of a naive recursive approach. **Output Example**: The function returns a single integer which is the Fibonacci number at the specified index `n`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>generate_random_integers</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a defined inclusive range.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Description | The total number of integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a straightforward way to generate a list of random integers. The logic proceeds as follows: 1. **Input Validation**: The function first validates the `count` parameter. If `count` is a negative number, it raises a `ValueError` because it's impossible to generate a negative number of items. 2. **Boundary Correction**: It checks if the `start` value is greater than the `end` value. If it is, the function swaps them to ensure that `start` is always the lower bound and `end...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>- This function requires the `random` module to be imported in the script. - The `count` parameter must be a non-negative integer. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` can appear in the output list. - If `start` is provided as a larger value than `end`, the function will automatically swap them internally. **Output Example**: A list containing integers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>shuffle_copy</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function returns a new list containing the same elements as the input list but in a randomized order, without modifying the original list.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>- `items`: `List[int]` - A list of integers that will be copied and shuffled.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list without causing side effects. The logic proceeds in three steps: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is the key step that ensures the original list passed to the function remains unchanged. 2. The standard library's `random.shuffle()` function is then called on the `copy`. This function shuffles the elements of the list *in-place*, rearranging the `copy` into a random permutation. 3. Finall...</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>- **Non-mutating:** The primary feature of this function is that it does not alter the original input list. It operates on a copy. - **Dependency:** This function requires the `random` module to be imported in the script where it is defined. - **Randomness:** The shuffle is pseudo-random. For reproducible results during testing, you can set the seed for the random number generator using `random.seed()` before calling this function. **Output Example**: A new list object containing the same ele...</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function creates and returns a new list with the elements of the input list arranged in a random order, leaving the original list unchanged.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>- **`items`** (`List[int]`): A list of integers that you want to shuffle.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process is executed in three main steps: 1. A shallow copy of the input `items` list is created using the `list()` constructor. This new list is stored in a variable named `copy`. This step is crucial for preserving the original list. 2. The `random.shuffle()` function is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearranging them into a random...</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>- This function is non-mutating, meaning the original list passed as the `items` parameter will not be changed. - The function depends on Python's standard `random` module. You must have `import random` at the beginning of your script to use this function. - The randomness is based on the default random number generator used by the `random` module. **Output Example**: The function returns a new list. For an input of `[1, 2, 3]`, a possible output could be:</t>
         </is>
       </c>
     </row>

--- a/random_module_two.xlsx
+++ b/random_module_two.xlsx
@@ -35,7 +35,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,12 +52,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E8F5"/>
         <bgColor rgb="00D9E8F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -88,12 +82,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -461,16 +449,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,204 +509,13 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>choose_random_item</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random element from a given list of strings.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>- **`items`** (`List[str]`): A list of strings from which one item will be randomly selected. This list must not be empty.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to choose a random item from a list. The logic proceeds as follows: 1. It first performs a validation check to determine if the input list `items` is empty. 2. If the list is empty, the condition `if not items:` evaluates to `True`, and the function raises a `ValueError` with the message "items must not be empty". This prevents errors that would otherwise occur when trying to select an item from an empty sequence. 3. If the list contains one or more elements,...</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>- The input list `items` must contain at least one element. Providing an empty list will result in a `ValueError`. - This function requires the `random` module to be imported in the script where it is used. - The selection is uniform, meaning every item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list. For example: `'banana'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>second_largest(nums)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>The `second_largest` function finds and returns the second-largest number from a list of numbers.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>- `nums` (list): A list of numbers (integers or floats) from which to find the second-largest value.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a reliable way to determine the second-largest value in a list by first removing any duplicate entries. The function begins by converting the input `nums` list into a `set` to eliminate duplicate values, and then converts it back into a `list` named `unique_nums`. Next, it sorts `unique_nums` in ascending order using the `sort()` method. After sorting, the largest number will be at the end of the list, and the second-largest will be the second-to-last element. Finally, ...</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>- The function correctly handles lists with duplicate numbers by considering only the unique values. - If the input list contains fewer than two unique numbers (e.g., `[5]`, `[8, 8, 8]`, or `[]`), the function will return `None`. - The input list can contain a mix of integers and floats. - The original input list `nums` is not modified by the function. **Output Example**: A numeric value (integer or float) or `None`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>count_even_odd(numbers)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>The `count_even_odd` function iterates through a list of integers and counts how many are even and how many are odd.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>* **`numbers`** (`list` of `int`): A list or other iterable containing the integers to be evaluated.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a straightforward way to tally even and odd numbers within a collection. It initializes two counter variables, `even` and `odd`, to zero. The function then enters a `for` loop that iterates over each element, referred to as `num`, in the input `numbers` list. Inside the loop, it uses the modulo operator (`%`) to check if `num` is divisible by 2. - If `num % 2` equals `0`, the number is even, and the `even` counter is incremented by one. - If the result is not `0`, the n...</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>- The input `numbers` must be an iterable containing numeric types that support the modulo operator. - The function will raise a `TypeError` if it encounters a non-numeric type within the list during the check. - The returned value is always a tuple of two integers: `(count_of_even, count_of_odd)`. **Output Example**: A tuple containing two integers. `(2, 3)`</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>fibonacci</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>- `n` (int): The 0-based index of the Fibonacci number to be computed.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a memory-efficient way to calculate a Fibonacci number. The Fibonacci sequence starts with 0 and 1, and each subsequent number is the sum of the two preceding ones (e.g., 0, 1, 1, 2, 3, 5, 8...). The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbe...</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>- The index `n` is 0-based. For example, `fibonacci(0)` returns `0`, and `fibonacci(1)` returns `1`. - The function will raise a `ValueError` if a negative integer is provided as the argument. - This iterative implementation is efficient for large values of `n` as it avoids the overhead and potential stack overflow of a naive recursive approach. **Output Example**: The function returns a single integer which is the Fibonacci number at the specified index `n`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>generate_random_integers</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a defined inclusive range.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Description | The total number of integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a straightforward way to generate a list of random integers. The logic proceeds as follows: 1. **Input Validation**: The function first validates the `count` parameter. If `count` is a negative number, it raises a `ValueError` because it's impossible to generate a negative number of items. 2. **Boundary Correction**: It checks if the `start` value is greater than the `end` value. If it is, the function swaps them to ensure that `start` is always the lower bound and `end...</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>- This function requires the `random` module to be imported in the script. - The `count` parameter must be a non-negative integer. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` can appear in the output list. - If `start` is provided as a larger value than `end`, the function will automatically swap them internally. **Output Example**: A list containing integers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>shuffle_copy</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function creates and returns a new list with the elements of the input list arranged in a random order, leaving the original list unchanged.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>- **`items`** (`List[int]`): A list of integers that you want to shuffle.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process is executed in three main steps: 1. A shallow copy of the input `items` list is created using the `list()` constructor. This new list is stored in a variable named `copy`. This step is crucial for preserving the original list. 2. The `random.shuffle()` function is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearranging them into a random...</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>- This function is non-mutating, meaning the original list passed as the `items` parameter will not be changed. - The function depends on Python's standard `random` module. You must have `import random` at the beginning of your script to use this function. - The randomness is based on the default random number generator used by the `random` module. **Output Example**: The function returns a new list. For an input of `[1, 2, 3]`, a possible output could be:</t>
-        </is>
-      </c>
+          <t>reverse_words(sentence)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
